--- a/3-Learning-and-Resources/3-3-Certification/FRM/Study-Plan.xlsx
+++ b/3-Learning-and-Resources/3-3-Certification/FRM/Study-Plan.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -306,6 +306,24 @@
     <t>Good luck on CFA!</t>
   </si>
   <si>
+    <t>In General</t>
+  </si>
+  <si>
+    <t>Weekdays</t>
+  </si>
+  <si>
+    <t>morning;work;night</t>
+  </si>
+  <si>
+    <t>2 hrs seperately</t>
+  </si>
+  <si>
+    <t>Weekends</t>
+  </si>
+  <si>
+    <t>3 hrs seperately</t>
+  </si>
+  <si>
     <t>Planed Hr</t>
   </si>
   <si>
@@ -343,6 +361,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Apple Color Emoji"/>
+        <charset val="134"/>
+      </rPr>
       <t>🚫</t>
     </r>
     <r>
@@ -366,7 +390,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -409,6 +433,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -564,7 +595,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,6 +604,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -764,7 +801,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -818,6 +855,68 @@
       <right style="medium">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color auto="1"/>
@@ -924,71 +1023,68 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1003,98 +1099,109 @@
     <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1106,11 +1213,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1125,7 +1265,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1164,7 +1304,139 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1451,18 +1723,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:O19"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
+  <dimension ref="B1:N24"/>
+  <sheetFormatPr defaultColWidth="8.24305555555556" defaultRowHeight="17.6"/>
   <cols>
     <col min="2" max="2" width="10.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="11.3333333333333" customWidth="1"/>
-    <col min="4" max="7" width="18.5" customWidth="1"/>
+    <col min="4" max="7" width="18.5069444444444" customWidth="1"/>
     <col min="8" max="12" width="18.1666666666667" customWidth="1"/>
-    <col min="13" max="14" width="15.3333333333333" customWidth="1"/>
-    <col min="15" max="15" width="45.8333333333333" customWidth="1"/>
+    <col min="13" max="13" width="15.3333333333333" customWidth="1"/>
+    <col min="14" max="14" width="45.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15">
+    <row r="1" ht="18.35"/>
+    <row r="2" ht="18.35" spans="2:14">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -1499,12 +1772,11 @@
       <c r="M2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="18.35" spans="2:15">
+    <row r="3" ht="18.75" spans="2:14">
       <c r="B3" s="12">
         <v>46141</v>
       </c>
@@ -1531,7 +1803,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="13">
-        <f>80</f>
+        <f t="shared" ref="I3:I9" si="1">80</f>
         <v>80</v>
       </c>
       <c r="J3" s="13">
@@ -1550,12 +1822,11 @@
         <f>G3+L3</f>
         <v>3.6</v>
       </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13" t="s">
+      <c r="N3" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="18.35" spans="2:15">
+    <row r="4" ht="18.75" spans="2:14">
       <c r="B4" s="12">
         <v>46142</v>
       </c>
@@ -1571,42 +1842,41 @@
         <v>2.4</v>
       </c>
       <c r="F4" s="13">
-        <f t="shared" ref="F4:F12" si="1">D4*E4</f>
+        <f t="shared" ref="F4:F12" si="2">D4*E4</f>
         <v>96</v>
       </c>
       <c r="G4" s="13">
-        <f t="shared" ref="G4:G12" si="2">F4/60</f>
+        <f t="shared" ref="G4:G12" si="3">F4/60</f>
         <v>1.6</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="13">
-        <f>80</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="J4" s="13">
-        <f t="shared" ref="J4:J18" si="3">1.5</f>
+        <f t="shared" ref="J4:J18" si="4">1.5</f>
         <v>1.5</v>
       </c>
       <c r="K4" s="13">
-        <f t="shared" ref="K4:K18" si="4">I4*J4</f>
+        <f t="shared" ref="K4:K18" si="5">I4*J4</f>
         <v>120</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" ref="L4:L18" si="5">K4/60</f>
+        <f t="shared" ref="L4:L18" si="6">K4/60</f>
         <v>2</v>
       </c>
       <c r="M4" s="13">
-        <f t="shared" ref="M4:M18" si="6">G4+L4</f>
+        <f t="shared" ref="M4:M18" si="7">G4+L4</f>
         <v>3.6</v>
       </c>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13" t="s">
+      <c r="N4" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="18.35" spans="2:15">
+    <row r="5" ht="18.75" spans="2:14">
       <c r="B5" s="12">
         <v>46143</v>
       </c>
@@ -1621,42 +1891,41 @@
         <v>2.4</v>
       </c>
       <c r="F5" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="G5" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="13">
-        <f>80</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="J5" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K5" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>120</v>
       </c>
       <c r="L5" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="M5" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13" t="s">
+      <c r="N5" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="18.35" spans="2:15">
+    <row r="6" ht="18.75" spans="2:14">
       <c r="B6" s="12">
         <v>46144</v>
       </c>
@@ -1671,11 +1940,11 @@
         <v>2.4</v>
       </c>
       <c r="F6" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="G6" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
       <c r="H6" s="13" t="s">
@@ -1686,27 +1955,26 @@
         <v>120</v>
       </c>
       <c r="J6" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K6" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>180</v>
       </c>
       <c r="L6" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="M6" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.6</v>
       </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13" t="s">
+      <c r="N6" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:15">
+    <row r="7" ht="18.35" spans="2:14">
       <c r="B7" s="12">
         <v>46145</v>
       </c>
@@ -1721,11 +1989,11 @@
         <v>2.4</v>
       </c>
       <c r="F7" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="G7" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
       <c r="H7" s="13" t="s">
@@ -1736,27 +2004,26 @@
         <v>180</v>
       </c>
       <c r="J7" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K7" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="L7" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
       <c r="M7" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.1</v>
       </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13" t="s">
+      <c r="N7" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" ht="18.35" spans="2:15">
+    <row r="8" ht="18.75" spans="2:14">
       <c r="B8" s="12">
         <v>46146</v>
       </c>
@@ -1771,42 +2038,41 @@
         <v>2.4</v>
       </c>
       <c r="F8" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="G8" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="13">
-        <f>80</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="J8" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K8" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>120</v>
       </c>
       <c r="L8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="M8" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13" t="s">
+      <c r="N8" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="18.35" spans="2:15">
+    <row r="9" ht="18.75" spans="2:14">
       <c r="B9" s="12">
         <v>46147</v>
       </c>
@@ -1821,42 +2087,41 @@
         <v>2.4</v>
       </c>
       <c r="F9" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="G9" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="13">
-        <f>80</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="J9" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K9" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>120</v>
       </c>
       <c r="L9" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="M9" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13" t="s">
+      <c r="N9" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="2:15">
+    <row r="10" ht="18.35" spans="2:14">
       <c r="B10" s="12">
         <v>46148</v>
       </c>
@@ -1871,42 +2136,41 @@
         <v>2.4</v>
       </c>
       <c r="F10" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="G10" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="13">
-        <f>180</f>
+        <f t="shared" ref="I10:I18" si="8">180</f>
         <v>180</v>
       </c>
       <c r="J10" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K10" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="L10" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
       <c r="M10" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.1</v>
       </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13" t="s">
+      <c r="N10" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:15">
+    <row r="11" ht="18.35" spans="2:14">
       <c r="B11" s="12">
         <v>46149</v>
       </c>
@@ -1921,11 +2185,11 @@
         <v>2.4</v>
       </c>
       <c r="F11" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="G11" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
       <c r="H11" s="13" t="s">
@@ -1936,27 +2200,26 @@
         <v>100</v>
       </c>
       <c r="J11" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K11" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
       <c r="L11" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
       <c r="M11" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.1</v>
       </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13" t="s">
+      <c r="N11" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="2:15">
+    <row r="12" ht="18.35" spans="2:14">
       <c r="B12" s="12">
         <v>46150</v>
       </c>
@@ -1971,11 +2234,11 @@
         <v>2.4</v>
       </c>
       <c r="F12" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="G12" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
       <c r="H12" s="13" t="s">
@@ -1986,27 +2249,26 @@
         <v>100</v>
       </c>
       <c r="J12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
       <c r="L12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
       <c r="M12" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.1</v>
       </c>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13" t="s">
+      <c r="N12" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="2:15">
+    <row r="13" ht="18.35" spans="2:14">
       <c r="B13" s="12">
         <v>46151</v>
       </c>
@@ -2016,9 +2278,9 @@
       <c r="D13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
       <c r="H13" s="13" t="s">
         <v>36</v>
       </c>
@@ -2027,27 +2289,26 @@
         <v>40</v>
       </c>
       <c r="J13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K13" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="L13" s="13">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="M13" s="13">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13" t="s">
+      <c r="M13" s="13">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N13" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="2:15">
+    <row r="14" ht="18.35" spans="2:14">
       <c r="B14" s="12">
         <v>46152</v>
       </c>
@@ -2064,31 +2325,30 @@
         <v>39</v>
       </c>
       <c r="I14" s="13">
-        <f>180</f>
+        <f t="shared" si="8"/>
         <v>180</v>
       </c>
       <c r="J14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K14" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="L14" s="13">
-        <f t="shared" si="5"/>
-        <v>4.5</v>
-      </c>
-      <c r="M14" s="13">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13" t="s">
+      <c r="M14" s="13">
+        <f t="shared" si="7"/>
+        <v>4.5</v>
+      </c>
+      <c r="N14" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" ht="18.35" spans="2:14">
       <c r="B15" s="12">
         <v>46153</v>
       </c>
@@ -2105,31 +2365,30 @@
         <v>21</v>
       </c>
       <c r="I15" s="13">
-        <f>180</f>
+        <f t="shared" si="8"/>
         <v>180</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="L15" s="13">
-        <f t="shared" si="5"/>
-        <v>4.5</v>
-      </c>
-      <c r="M15" s="13">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13" t="s">
+      <c r="M15" s="13">
+        <f t="shared" si="7"/>
+        <v>4.5</v>
+      </c>
+      <c r="N15" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="2:15">
+    <row r="16" ht="18.35" spans="2:14">
       <c r="B16" s="12">
         <v>46154</v>
       </c>
@@ -2146,31 +2405,30 @@
         <v>42</v>
       </c>
       <c r="I16" s="13">
-        <f>180</f>
+        <f t="shared" si="8"/>
         <v>180</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K16" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="L16" s="13">
-        <f t="shared" si="5"/>
-        <v>4.5</v>
-      </c>
-      <c r="M16" s="13">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13" t="s">
+      <c r="M16" s="13">
+        <f t="shared" si="7"/>
+        <v>4.5</v>
+      </c>
+      <c r="N16" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" ht="18.35" spans="2:14">
       <c r="B17" s="12">
         <v>46155</v>
       </c>
@@ -2187,31 +2445,30 @@
         <v>21</v>
       </c>
       <c r="I17" s="13">
-        <f>180</f>
+        <f t="shared" si="8"/>
         <v>180</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K17" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="L17" s="13">
-        <f t="shared" si="5"/>
-        <v>4.5</v>
-      </c>
-      <c r="M17" s="13">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13" t="s">
+      <c r="M17" s="13">
+        <f t="shared" si="7"/>
+        <v>4.5</v>
+      </c>
+      <c r="N17" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" ht="18.35" spans="2:14">
       <c r="B18" s="12">
         <v>46156</v>
       </c>
@@ -2228,31 +2485,30 @@
         <v>45</v>
       </c>
       <c r="I18" s="13">
-        <f>180</f>
+        <f t="shared" si="8"/>
         <v>180</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="K18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="L18" s="13">
-        <f t="shared" si="5"/>
-        <v>4.5</v>
-      </c>
-      <c r="M18" s="13">
         <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13" t="s">
+      <c r="M18" s="13">
+        <f t="shared" si="7"/>
+        <v>4.5</v>
+      </c>
+      <c r="N18" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" ht="18.35" spans="2:14">
       <c r="B19" s="12">
         <v>46157</v>
       </c>
@@ -2265,23 +2521,60 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
       <c r="M19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="16" t="s">
+      <c r="N19" s="15" t="s">
         <v>49</v>
       </c>
     </row>
+    <row r="21" ht="18.35"/>
+    <row r="22" ht="21.15" spans="2:14">
+      <c r="B22" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" ht="18.35" spans="2:14">
+      <c r="B24" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="3">
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+  </mergeCells>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -2290,318 +2583,318 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B2:F20"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="17.6" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.24305555555556" defaultRowHeight="17.6" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="3.88888888888889" customWidth="1"/>
-    <col min="4" max="4" width="10.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="4.72222222222222" customWidth="1"/>
-    <col min="6" max="6" width="52" customWidth="1"/>
+    <col min="2" max="2" width="13.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.2777777777778" customWidth="1"/>
+    <col min="4" max="4" width="16.4861111111111" customWidth="1"/>
+    <col min="5" max="5" width="11.7986111111111" customWidth="1"/>
+    <col min="6" max="6" width="58.2430555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="18.35"/>
-    <row r="3" ht="31.75" spans="2:6">
-      <c r="B3" s="1" t="s">
+    <row r="3" ht="18.35" spans="2:6">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="3">
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" ht="18.35" spans="2:6">
+      <c r="B4" s="5">
         <v>46141</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="C4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="6">
         <v>3.6</v>
       </c>
       <c r="E4" s="7">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="3">
+      <c r="F4" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" ht="18.35" spans="2:6">
+      <c r="B5" s="5">
         <v>46142</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="6">
         <v>3.6</v>
       </c>
       <c r="E5" s="7">
         <v>6</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="3">
+      <c r="F5" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" ht="18.35" spans="2:6">
+      <c r="B6" s="5">
         <v>46143</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="C6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="6">
         <v>3.6</v>
       </c>
       <c r="E6" s="7">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="3">
+      <c r="F6" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" ht="18.35" spans="2:6">
+      <c r="B7" s="5">
         <v>46144</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="6">
         <v>4.6</v>
       </c>
       <c r="E7" s="7">
         <v>8</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="3">
+      <c r="F7" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" ht="18.35" spans="2:6">
+      <c r="B8" s="5">
         <v>46145</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="6">
         <v>6.1</v>
       </c>
       <c r="E8" s="7">
         <v>8</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="3">
+      <c r="F8" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" ht="18.35" spans="2:6">
+      <c r="B9" s="5">
         <v>46146</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="6">
         <v>3.6</v>
       </c>
       <c r="E9" s="7">
         <v>6</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="3">
+      <c r="F9" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" ht="18.35" spans="2:6">
+      <c r="B10" s="5">
         <v>46147</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="6">
         <v>3.6</v>
       </c>
       <c r="E10" s="7">
         <v>6</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="3">
+      <c r="F10" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" ht="18.35" spans="2:6">
+      <c r="B11" s="5">
         <v>46148</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="6">
         <v>6.1</v>
       </c>
       <c r="E11" s="7">
         <v>6</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="3">
+      <c r="F11" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" ht="18.35" spans="2:6">
+      <c r="B12" s="5">
         <v>46149</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="6">
         <v>4.1</v>
       </c>
       <c r="E12" s="7">
         <v>6</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="3">
+      <c r="F12" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" ht="18.35" spans="2:6">
+      <c r="B13" s="5">
         <v>46150</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="6">
         <v>4.1</v>
       </c>
       <c r="E13" s="7">
         <v>6</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="3">
+      <c r="F13" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" ht="18.35" spans="2:6">
+      <c r="B14" s="5">
         <v>46151</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="6">
         <v>1</v>
       </c>
       <c r="E14" s="7">
         <v>1</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="3">
+      <c r="F14" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" ht="18.35" spans="2:6">
+      <c r="B15" s="5">
         <v>46152</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="6">
         <v>4.5</v>
       </c>
       <c r="E15" s="7">
         <v>6</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="3">
+      <c r="F15" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" ht="18.35" spans="2:6">
+      <c r="B16" s="5">
         <v>46153</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="6">
         <v>4.5</v>
       </c>
       <c r="E16" s="7">
         <v>6</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="3">
+      <c r="F16" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" ht="18.35" spans="2:6">
+      <c r="B17" s="5">
         <v>46154</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="6">
         <v>4.5</v>
       </c>
       <c r="E17" s="7">
         <v>6</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="3">
+      <c r="F17" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" ht="18.35" spans="2:6">
+      <c r="B18" s="5">
         <v>46155</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="6">
         <v>4.5</v>
       </c>
       <c r="E18" s="7">
         <v>6</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="3">
+      <c r="F18" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" ht="18.35" spans="2:6">
+      <c r="B19" s="5">
         <v>46156</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="6">
         <v>4.5</v>
       </c>
       <c r="E19" s="7">
         <v>6</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="3">
+      <c r="F19" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" ht="18.35" spans="2:6">
+      <c r="B20" s="5">
         <v>46157</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="C20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
